--- a/outputs/423-16.xlsx
+++ b/outputs/423-16.xlsx
@@ -528,63 +528,63 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="5" fillId="2" borderId="1" xfId="24" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="168" fontId="5" fillId="2" borderId="1" xfId="24" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="5" fillId="2" borderId="1" xfId="24" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="168" fontId="5" fillId="2" borderId="1" xfId="24" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="24" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="24" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="24" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="24" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="24" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="24" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="24" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="24" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="24" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="24" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="24" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="24" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="3" borderId="2" xfId="24" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="3" borderId="2" xfId="24" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="3" borderId="3" xfId="24" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="3" borderId="3" xfId="24" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="5" fillId="2" borderId="4" xfId="24" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="168" fontId="5" fillId="2" borderId="4" xfId="24" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="5" xfId="24" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="5" xfId="24" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="5" fillId="2" borderId="4" xfId="24" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="168" fontId="5" fillId="2" borderId="4" xfId="24" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -592,107 +592,107 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="4" borderId="5" xfId="24" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="4" borderId="5" xfId="24" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="5" borderId="6" xfId="24" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="10" fillId="5" borderId="6" xfId="24" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="169" fontId="8" fillId="6" borderId="4" xfId="24" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="169" fontId="8" fillId="6" borderId="4" xfId="24" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="6" borderId="5" xfId="24" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="6" borderId="5" xfId="24" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="169" fontId="8" fillId="4" borderId="4" xfId="24" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="169" fontId="8" fillId="4" borderId="4" xfId="24" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="4" borderId="5" xfId="24" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="4" borderId="5" xfId="24" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="170" fontId="5" fillId="0" borderId="5" xfId="24" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="170" fontId="5" fillId="0" borderId="5" xfId="24" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="171" fontId="5" fillId="0" borderId="5" xfId="24" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="171" fontId="5" fillId="0" borderId="5" xfId="24" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="11" fillId="0" borderId="4" xfId="24" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="168" fontId="11" fillId="0" borderId="4" xfId="24" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="4" borderId="5" xfId="24" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="4" borderId="5" xfId="24" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="5" xfId="24" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="5" xfId="24" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="5" fillId="2" borderId="4" xfId="24" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="168" fontId="8" fillId="0" borderId="4" xfId="24" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="168" fontId="8" fillId="0" borderId="4" xfId="24" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="168" fontId="5" fillId="2" borderId="4" xfId="24" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="168" fontId="8" fillId="0" borderId="4" xfId="24" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="168" fontId="8" fillId="0" borderId="4" xfId="24" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="24" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="24" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="169" fontId="8" fillId="2" borderId="4" xfId="24" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="169" fontId="8" fillId="2" borderId="4" xfId="24" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="11" fillId="0" borderId="4" xfId="24" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="4" xfId="24" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="24" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="168" fontId="5" fillId="0" borderId="4" xfId="24" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="167" fontId="8" fillId="7" borderId="7" xfId="26" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="168" fontId="11" fillId="0" borderId="4" xfId="24" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="4" xfId="24" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="24" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="168" fontId="5" fillId="0" borderId="4" xfId="24" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="8" fillId="7" borderId="7" xfId="26" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="12" fillId="8" borderId="0" xfId="24" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="172" fontId="8" fillId="7" borderId="8" xfId="24" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="167" fontId="12" fillId="8" borderId="0" xfId="24" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="172" fontId="8" fillId="7" borderId="8" xfId="24" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="173" fontId="8" fillId="4" borderId="5" xfId="24" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="173" fontId="8" fillId="4" borderId="5" xfId="24" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="5" fillId="0" borderId="9" xfId="24" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="168" fontId="5" fillId="0" borderId="9" xfId="24" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="173" fontId="8" fillId="4" borderId="10" xfId="24" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="173" fontId="8" fillId="4" borderId="10" xfId="24" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -952,110 +952,105 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:AH1"/>
+  <dimension ref="A1:AC1"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="7.57"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="12.43"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="8.14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="7"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="17.86"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="19.14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="7.57"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="12.43"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="8.14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="7"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="17.86"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="19.14"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="H1" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="3" t="s">
+      <c r="I1" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="3" t="s">
+      <c r="J1" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="3" t="s">
+      <c r="K1" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="3" t="s">
+      <c r="L1" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="3" t="s">
+      <c r="M1" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="3" t="s">
+      <c r="N1" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="3" t="s">
+      <c r="O1" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="3" t="s">
+      <c r="P1" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="3" t="s">
+      <c r="Q1" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="3" t="s">
+      <c r="R1" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="S1" s="3" t="s">
+      <c r="S1" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="T1" s="3" t="s">
+      <c r="T1" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="U1" s="3" t="s">
+      <c r="U1" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="V1" s="3" t="s">
+      <c r="V1" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="W1" s="3" t="s">
+      <c r="W1" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="X1" s="3" t="s">
+      <c r="X1" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="Y1" s="3" t="s">
+      <c r="Y1" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="Z1" s="3" t="s">
+      <c r="Z1" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="AA1" s="3" t="s">
+      <c r="AA1" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="AB1" s="3" t="s">
+      <c r="AB1" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="AC1" s="3" t="s">
+      <c r="AC1" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="AD1" s="4"/>
-      <c r="AE1" s="4"/>
-      <c r="AF1" s="4"/>
-      <c r="AG1" s="4"/>
-      <c r="AH1" s="4"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
